--- a/data/results/predictions_2025_with_nac.xlsx
+++ b/data/results/predictions_2025_with_nac.xlsx
@@ -576,12 +576,12 @@
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
+          <t>n_sa</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
           <t>dl_mois</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>n_sa</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
@@ -789,10 +789,10 @@
         <v>12</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF3" t="n">
         <v>1.015263357974515</v>
@@ -893,10 +893,10 @@
         <v>12</v>
       </c>
       <c r="AD4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF4" t="n">
         <v>5.816117950780943</v>
@@ -997,10 +997,10 @@
         <v>12</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF5" t="n">
         <v>2.645385485139431</v>
@@ -1101,10 +1101,10 @@
         <v>12</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF6" t="n">
         <v>1.92637399289188</v>
@@ -1205,10 +1205,10 @@
         <v>12</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF7" t="n">
         <v>2.421531102426449</v>
@@ -1309,10 +1309,10 @@
         <v>12</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF8" t="n">
         <v>6.514217593890724</v>
@@ -1413,10 +1413,10 @@
         <v>12</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF9" t="n">
         <v>0.06033095084630302</v>
@@ -1517,10 +1517,10 @@
         <v>12</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF10" t="n">
         <v>0.09511895533931836</v>
@@ -1621,10 +1621,10 @@
         <v>12</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF11" t="n">
         <v>2.458356601304836</v>
@@ -1713,7 +1713,7 @@
         <v>0.4083389961667553</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.4518996432921961</v>
+        <v>0.4518996432921963</v>
       </c>
       <c r="AA12" t="n">
         <v>0.3465983539059778</v>
@@ -1725,10 +1725,10 @@
         <v>12</v>
       </c>
       <c r="AD12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0.322150101351609</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.628069217836969</v>
+        <v>1.628069217836968</v>
       </c>
       <c r="AA13" t="n">
         <v>1.746352239712419</v>
@@ -1829,10 +1829,10 @@
         <v>12</v>
       </c>
       <c r="AD13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF13" t="n">
         <v>1.582117413237473</v>
@@ -1933,10 +1933,10 @@
         <v>12</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2037,10 +2037,10 @@
         <v>12</v>
       </c>
       <c r="AD15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF15" t="n">
         <v>0.08281913424837395</v>
@@ -2129,7 +2129,7 @@
         <v>0.3375670713282506</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.3025958371938966</v>
+        <v>0.3025958371938967</v>
       </c>
       <c r="AA16" t="n">
         <v>0.1602292754400629</v>
@@ -2141,10 +2141,10 @@
         <v>12</v>
       </c>
       <c r="AD16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF16" t="n">
         <v>1.053409758480021</v>
@@ -2349,10 +2349,10 @@
         <v>12</v>
       </c>
       <c r="AD18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF18" t="n">
         <v>5.157087096445426</v>
@@ -2453,10 +2453,10 @@
         <v>12</v>
       </c>
       <c r="AD19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF19" t="n">
         <v>4.167413342029037</v>
@@ -2545,7 +2545,7 @@
         <v>0.0817186292964901</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.3574574098393837</v>
+        <v>0.3574574098393836</v>
       </c>
       <c r="AA20" t="n">
         <v>0.2973893756866849</v>
@@ -2649,7 +2649,7 @@
         <v>0.5240093760089105</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.9897506968886854</v>
+        <v>0.9897506968886853</v>
       </c>
       <c r="AA21" t="n">
         <v>0.597309060882465</v>
@@ -2661,10 +2661,10 @@
         <v>12</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -2765,10 +2765,10 @@
         <v>12</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF22" t="n">
         <v>2.429678294133283</v>
@@ -2857,7 +2857,7 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.2516151070992835</v>
+        <v>0.2516151070992834</v>
       </c>
       <c r="AA23" t="n">
         <v>0.2813828041131907</v>
@@ -2869,10 +2869,10 @@
         <v>12</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -2961,7 +2961,7 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.2516151070992835</v>
+        <v>0.2516151070992834</v>
       </c>
       <c r="AA24" t="n">
         <v>0.2813828041131907</v>
@@ -2973,10 +2973,10 @@
         <v>12</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3065,7 +3065,7 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.1621182081205489</v>
+        <v>0.1621182081205488</v>
       </c>
       <c r="AA25" t="n">
         <v>0.241483064966427</v>
@@ -3077,10 +3077,10 @@
         <v>12</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3169,7 +3169,7 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.1621182081205489</v>
+        <v>0.1621182081205488</v>
       </c>
       <c r="AA26" t="n">
         <v>0.241483064966427</v>
@@ -3181,10 +3181,10 @@
         <v>12</v>
       </c>
       <c r="AD26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3286,10 +3286,10 @@
         <v>12</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF27" t="n">
         <v>1.15629696578256</v>
@@ -3379,7 +3379,7 @@
         <v>0.51840248615724</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.7313392604033555</v>
+        <v>0.7313392604033554</v>
       </c>
       <c r="AA28" t="n">
         <v>0.9778697252634824</v>
@@ -3391,10 +3391,10 @@
         <v>12</v>
       </c>
       <c r="AD28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -3496,10 +3496,10 @@
         <v>12</v>
       </c>
       <c r="AD29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -3600,10 +3600,10 @@
         <v>12</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF30" t="n">
         <v>0.04695386486904618</v>
@@ -3692,7 +3692,7 @@
         <v>0.06286708542555236</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.2924051517847328</v>
+        <v>0.2924051517847326</v>
       </c>
       <c r="AA31" t="n">
         <v>0.2335416284659564</v>
@@ -3704,10 +3704,10 @@
         <v>12</v>
       </c>
       <c r="AD31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF31" t="n">
         <v>0.0778472094886522</v>
@@ -3808,10 +3808,10 @@
         <v>12</v>
       </c>
       <c r="AD32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF32" t="n">
         <v>1.013897105840106</v>
@@ -4016,10 +4016,10 @@
         <v>12</v>
       </c>
       <c r="AD34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF34" t="n">
         <v>0.01296242790491142</v>
@@ -4120,10 +4120,10 @@
         <v>12</v>
       </c>
       <c r="AD35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF35" t="n">
         <v>0.09511895533931836</v>
@@ -4224,10 +4224,10 @@
         <v>12</v>
       </c>
       <c r="AD36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF36" t="n">
         <v>1.45197126005289</v>
@@ -4316,7 +4316,7 @@
         <v>1.110042476458525</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.9144903934393898</v>
+        <v>0.9144903934393899</v>
       </c>
       <c r="AA37" t="n">
         <v>0.4558067539373578</v>
@@ -4328,10 +4328,10 @@
         <v>12</v>
       </c>
       <c r="AD37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -4432,10 +4432,10 @@
         <v>12</v>
       </c>
       <c r="AD38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF38" t="n">
         <v>1.047301405744378</v>
@@ -4524,7 +4524,7 @@
         <v>0.1527384036386698</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.09386388924025851</v>
+        <v>0.0938638892402585</v>
       </c>
       <c r="AA39" t="n">
         <v>0.09419155909548772</v>
@@ -4536,10 +4536,10 @@
         <v>12</v>
       </c>
       <c r="AD39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF39" t="n">
         <v>1.031397186365163</v>
@@ -4640,10 +4640,10 @@
         <v>12</v>
       </c>
       <c r="AD40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -4732,7 +4732,7 @@
         <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.1624984409759251</v>
+        <v>0.162498440975925</v>
       </c>
       <c r="AA41" t="n">
         <v>0.1460224792229973</v>
@@ -4744,10 +4744,10 @@
         <v>12</v>
       </c>
       <c r="AD41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -4836,7 +4836,7 @@
         <v>0.1184489749262798</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.09267858182794748</v>
+        <v>0.09267858182794747</v>
       </c>
       <c r="AA42" t="n">
         <v>0.2027358404252795</v>
@@ -4848,10 +4848,10 @@
         <v>12</v>
       </c>
       <c r="AD42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF42" t="n">
         <v>0.06757861347509309</v>
@@ -4940,7 +4940,7 @@
         <v>0.1184489749262798</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.09267858182794748</v>
+        <v>0.09267858182794747</v>
       </c>
       <c r="AA43" t="n">
         <v>0.2027358404252795</v>
@@ -4952,10 +4952,10 @@
         <v>12</v>
       </c>
       <c r="AD43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF43" t="n">
         <v>0.06757861347509309</v>
@@ -5044,7 +5044,7 @@
         <v>0.2914530117660564</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.3967223898846517</v>
+        <v>0.3967223898846518</v>
       </c>
       <c r="AA44" t="n">
         <v>0.3862156218237958</v>
@@ -5056,10 +5056,10 @@
         <v>12</v>
       </c>
       <c r="AD44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF44" t="n">
         <v>1.128738540607932</v>
@@ -5160,10 +5160,10 @@
         <v>12</v>
       </c>
       <c r="AD45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF45" t="n">
         <v>1.089967015357764</v>
@@ -5264,10 +5264,10 @@
         <v>12</v>
       </c>
       <c r="AD46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF46" t="n">
         <v>1.10574495685983</v>
@@ -5356,7 +5356,7 @@
         <v>0.1856888987677929</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.1977563995042144</v>
+        <v>0.1977563995042145</v>
       </c>
       <c r="AA47" t="n">
         <v>0.3355645774173374</v>
@@ -5368,10 +5368,10 @@
         <v>12</v>
       </c>
       <c r="AD47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF47" t="n">
         <v>2.111854859139112</v>
@@ -5472,10 +5472,10 @@
         <v>12</v>
       </c>
       <c r="AD48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF48" t="n">
         <v>1.039341549858214</v>
@@ -5576,10 +5576,10 @@
         <v>12</v>
       </c>
       <c r="AD49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF49" t="n">
         <v>1.039341549858214</v>
@@ -5680,10 +5680,10 @@
         <v>12</v>
       </c>
       <c r="AD50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF50" t="n">
         <v>1.014765851738619</v>
@@ -5784,10 +5784,10 @@
         <v>12</v>
       </c>
       <c r="AD51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF51" t="n">
         <v>2.040749636394338</v>
@@ -5888,10 +5888,10 @@
         <v>12</v>
       </c>
       <c r="AD52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF52" t="n">
         <v>1.047301405744378</v>
@@ -5992,10 +5992,10 @@
         <v>12</v>
       </c>
       <c r="AD53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF53" t="n">
         <v>0.05473103164603321</v>
@@ -6096,10 +6096,10 @@
         <v>12</v>
       </c>
       <c r="AD54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF54" t="n">
         <v>2</v>
@@ -6200,10 +6200,10 @@
         <v>12</v>
       </c>
       <c r="AD55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF55" t="n">
         <v>1.291721776762425</v>
@@ -6304,10 +6304,10 @@
         <v>12</v>
       </c>
       <c r="AD56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF56" t="n">
         <v>0.05429903399381697</v>
@@ -6396,7 +6396,7 @@
         <v>0.08296568068329485</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.04099696759531981</v>
+        <v>0.04099696759531982</v>
       </c>
       <c r="AA57" t="n">
         <v>0.08365643222110092</v>
@@ -6408,10 +6408,10 @@
         <v>12</v>
       </c>
       <c r="AD57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF57" t="n">
         <v>1.027885477407034</v>
@@ -6512,10 +6512,10 @@
         <v>12</v>
       </c>
       <c r="AD58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF58" t="n">
         <v>1.013897105840106</v>
@@ -6616,10 +6616,10 @@
         <v>12</v>
       </c>
       <c r="AD59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF59" t="n">
         <v>0.01432868003932031</v>
@@ -6720,10 +6720,10 @@
         <v>12</v>
       </c>
       <c r="AD60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF60" t="n">
         <v>0</v>
@@ -6824,10 +6824,10 @@
         <v>12</v>
       </c>
       <c r="AD61" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="AE61" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="AF61" t="n">
         <v>0</v>
@@ -6928,10 +6928,10 @@
         <v>12</v>
       </c>
       <c r="AD62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF62" t="n">
         <v>4</v>
@@ -7032,10 +7032,10 @@
         <v>12</v>
       </c>
       <c r="AD63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF63" t="n">
         <v>0</v>
@@ -7136,10 +7136,10 @@
         <v>12</v>
       </c>
       <c r="AD64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF64" t="n">
         <v>3.277307558952758</v>
@@ -7228,7 +7228,7 @@
         <v>0.291604280476669</v>
       </c>
       <c r="Z65" t="n">
-        <v>0.483925404331207</v>
+        <v>0.4839254043312071</v>
       </c>
       <c r="AA65" t="n">
         <v>0.3601253461693635</v>
@@ -7240,10 +7240,10 @@
         <v>12</v>
       </c>
       <c r="AD65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF65" t="n">
         <v>1.120041782056455</v>
@@ -7344,10 +7344,10 @@
         <v>12</v>
       </c>
       <c r="AD66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF66" t="n">
         <v>1.060017289456858</v>
@@ -7448,10 +7448,10 @@
         <v>12</v>
       </c>
       <c r="AD67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF67" t="n">
         <v>0.1432500414292879</v>
@@ -7552,10 +7552,10 @@
         <v>12</v>
       </c>
       <c r="AD68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF68" t="n">
         <v>0</v>
@@ -7656,10 +7656,10 @@
         <v>12</v>
       </c>
       <c r="AD69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF69" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>12</v>
       </c>
       <c r="AD70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF70" t="n">
         <v>0.1208478974528679</v>
@@ -7852,7 +7852,7 @@
         <v>0.5156820542417571</v>
       </c>
       <c r="Z71" t="n">
-        <v>0.1907977427046527</v>
+        <v>0.1907977427046526</v>
       </c>
       <c r="AA71" t="n">
         <v>0.2615832959779711</v>
@@ -7864,10 +7864,10 @@
         <v>12</v>
       </c>
       <c r="AD71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF71" t="n">
         <v>1.087194431992657</v>
@@ -7968,10 +7968,10 @@
         <v>12</v>
       </c>
       <c r="AD72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF72" t="n">
         <v>3.398990867237125</v>
@@ -8060,7 +8060,7 @@
         <v>1.771422519027422</v>
       </c>
       <c r="Z73" t="n">
-        <v>3.257566693124072</v>
+        <v>3.257566693124071</v>
       </c>
       <c r="AA73" t="n">
         <v>2.582084654829428</v>
@@ -8072,10 +8072,10 @@
         <v>12</v>
       </c>
       <c r="AD73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF73" t="n">
         <v>6.860694884943142</v>
@@ -8280,10 +8280,10 @@
         <v>12</v>
       </c>
       <c r="AD75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF75" t="n">
         <v>0</v>
@@ -8384,10 +8384,10 @@
         <v>12</v>
       </c>
       <c r="AD76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF76" t="n">
         <v>5.404906332848197</v>
@@ -8488,10 +8488,10 @@
         <v>12</v>
       </c>
       <c r="AD77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF77" t="n">
         <v>2.342978058528921</v>
@@ -8592,10 +8592,10 @@
         <v>12</v>
       </c>
       <c r="AD78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF78" t="n">
         <v>0</v>
@@ -8696,10 +8696,10 @@
         <v>12</v>
       </c>
       <c r="AD79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF79" t="n">
         <v>1.12011566473677</v>
@@ -8800,10 +8800,10 @@
         <v>12</v>
       </c>
       <c r="AD80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF80" t="n">
         <v>0.01750485786964884</v>
@@ -9008,10 +9008,10 @@
         <v>12</v>
       </c>
       <c r="AD82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF82" t="n">
         <v>0</v>
@@ -9112,10 +9112,10 @@
         <v>12</v>
       </c>
       <c r="AD83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF83" t="n">
         <v>0.01432868003932031</v>
@@ -9216,10 +9216,10 @@
         <v>12</v>
       </c>
       <c r="AD84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF84" t="n">
         <v>0.01750485786964884</v>
@@ -9320,10 +9320,10 @@
         <v>12</v>
       </c>
       <c r="AD85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF85" t="n">
         <v>0.01750485786964884</v>
@@ -9424,10 +9424,10 @@
         <v>12</v>
       </c>
       <c r="AD86" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF86" t="n">
         <v>1.016132103873028</v>
@@ -9516,7 +9516,7 @@
         <v>0.08440619928828968</v>
       </c>
       <c r="Z87" t="n">
-        <v>0.04651049909487494</v>
+        <v>0.04651049909487495</v>
       </c>
       <c r="AA87" t="n">
         <v>0.04240784043687944</v>
@@ -9528,10 +9528,10 @@
         <v>12</v>
       </c>
       <c r="AD87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF87" t="n">
         <v>1.014135946812293</v>
@@ -9632,10 +9632,10 @@
         <v>12</v>
       </c>
       <c r="AD88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF88" t="n">
         <v>1.087194431992657</v>
@@ -9736,10 +9736,10 @@
         <v>12</v>
       </c>
       <c r="AD89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF89" t="n">
         <v>0.05445074314027787</v>
@@ -9828,7 +9828,7 @@
         <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>0.03089918507443756</v>
+        <v>0.03089918507443757</v>
       </c>
       <c r="AA90" t="n">
         <v>0.04652610242674303</v>
@@ -9840,10 +9840,10 @@
         <v>12</v>
       </c>
       <c r="AD90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF90" t="n">
         <v>0.01550870080891431</v>
@@ -9944,10 +9944,10 @@
         <v>12</v>
       </c>
       <c r="AD91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF91" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
         <v>0.07489509402954736</v>
       </c>
       <c r="Z92" t="n">
-        <v>0.09038290226760327</v>
+        <v>0.09038290226760326</v>
       </c>
       <c r="AA92" t="n">
         <v>0.1536274598401464</v>
@@ -10048,10 +10048,10 @@
         <v>12</v>
       </c>
       <c r="AD92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF92" t="n">
         <v>0</v>
@@ -10152,10 +10152,10 @@
         <v>12</v>
       </c>
       <c r="AD93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF93" t="n">
         <v>0.06080263281841836</v>
@@ -10256,10 +10256,10 @@
         <v>12</v>
       </c>
       <c r="AD94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF94" t="n">
         <v>0.01432868003932031</v>
@@ -10348,7 +10348,7 @@
         <v>0.08787423625503737</v>
       </c>
       <c r="Z95" t="n">
-        <v>0.06551458686106991</v>
+        <v>0.0655145868610699</v>
       </c>
       <c r="AA95" t="n">
         <v>0.04652610242674303</v>
@@ -10360,10 +10360,10 @@
         <v>12</v>
       </c>
       <c r="AD95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF95" t="n">
         <v>0</v>
@@ -10452,7 +10452,7 @@
         <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>0.01977541499901621</v>
+        <v>0.0197754149990162</v>
       </c>
       <c r="AA96" t="n">
         <v>0.04839631161908282</v>
@@ -10464,10 +10464,10 @@
         <v>12</v>
       </c>
       <c r="AD96" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF96" t="n">
         <v>1.016132103873028</v>
@@ -10556,7 +10556,7 @@
         <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>0.01977541499901621</v>
+        <v>0.0197754149990162</v>
       </c>
       <c r="AA97" t="n">
         <v>0.04839631161908282</v>
@@ -10568,10 +10568,10 @@
         <v>12</v>
       </c>
       <c r="AD97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF97" t="n">
         <v>1.016132103873028</v>
@@ -10660,7 +10660,7 @@
         <v>0.02921454544914776</v>
       </c>
       <c r="Z98" t="n">
-        <v>0.08113622718405367</v>
+        <v>0.08113622718405365</v>
       </c>
       <c r="AA98" t="n">
         <v>0.09008780582267772</v>
@@ -10672,10 +10672,10 @@
         <v>12</v>
       </c>
       <c r="AD98" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF98" t="n">
         <v>1.030029268607559</v>
@@ -10764,7 +10764,7 @@
         <v>0.03065506405414253</v>
       </c>
       <c r="Z99" t="n">
-        <v>0.09535133451763254</v>
+        <v>0.09535133451763256</v>
       </c>
       <c r="AA99" t="n">
         <v>0.1354716697730992</v>
@@ -10776,10 +10776,10 @@
         <v>12</v>
       </c>
       <c r="AD99" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF99" t="n">
         <v>1.0451572232577</v>
@@ -10868,7 +10868,7 @@
         <v>0.3565212907724208</v>
       </c>
       <c r="Z100" t="n">
-        <v>0.06447105072285329</v>
+        <v>0.06447105072285331</v>
       </c>
       <c r="AA100" t="n">
         <v>0.1263671711728773</v>
@@ -10880,10 +10880,10 @@
         <v>12</v>
       </c>
       <c r="AD100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF100" t="n">
         <v>0</v>
@@ -10972,7 +10972,7 @@
         <v>0.3565212907724208</v>
       </c>
       <c r="Z101" t="n">
-        <v>0.06447105072285329</v>
+        <v>0.06447105072285331</v>
       </c>
       <c r="AA101" t="n">
         <v>0.1263671711728773</v>
@@ -10984,10 +10984,10 @@
         <v>12</v>
       </c>
       <c r="AD101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF101" t="n">
         <v>0</v>
@@ -11088,10 +11088,10 @@
         <v>12</v>
       </c>
       <c r="AD102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF102" t="n">
         <v>0.01550870080891431</v>
@@ -11180,7 +11180,7 @@
         <v>0.3907646195208626</v>
       </c>
       <c r="Z103" t="n">
-        <v>0.2392271886334304</v>
+        <v>0.2392271886334303</v>
       </c>
       <c r="AA103" t="n">
         <v>0.3899741476251199</v>
@@ -11192,10 +11192,10 @@
         <v>12</v>
       </c>
       <c r="AD103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF103" t="n">
         <v>1.129991382541707</v>
@@ -11296,10 +11296,10 @@
         <v>12</v>
       </c>
       <c r="AD104" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF104" t="n">
         <v>1.1390966240221</v>
@@ -11388,7 +11388,7 @@
         <v>0.08469969916666881</v>
       </c>
       <c r="Z105" t="n">
-        <v>0.04512981201016617</v>
+        <v>0.04512981201016619</v>
       </c>
       <c r="AA105" t="n">
         <v>0.08777469421096452</v>
@@ -11400,10 +11400,10 @@
         <v>12</v>
       </c>
       <c r="AD105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF105" t="n">
         <v>0.02925823140365491</v>
@@ -11492,7 +11492,7 @@
         <v>0.03353610126413203</v>
       </c>
       <c r="Z106" t="n">
-        <v>0.04984271741778463</v>
+        <v>0.04984271741778462</v>
       </c>
       <c r="AA106" t="n">
         <v>0.04756872505273846</v>
@@ -11504,10 +11504,10 @@
         <v>12</v>
       </c>
       <c r="AD106" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF106" t="n">
         <v>1.015856241684246</v>
@@ -11608,10 +11608,10 @@
         <v>12</v>
       </c>
       <c r="AD107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF107" t="n">
         <v>1.07469277657893</v>
@@ -11700,7 +11700,7 @@
         <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>0.01977541499901621</v>
+        <v>0.0197754149990162</v>
       </c>
       <c r="AA108" t="n">
         <v>0.04839631161908282</v>
@@ -11712,10 +11712,10 @@
         <v>12</v>
       </c>
       <c r="AD108" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF108" t="n">
         <v>1.016132103873028</v>
@@ -11804,7 +11804,7 @@
         <v>0.03353610126413203</v>
       </c>
       <c r="Z109" t="n">
-        <v>0.04984271741778463</v>
+        <v>0.04984271741778462</v>
       </c>
       <c r="AA109" t="n">
         <v>0.04756872505273846</v>
@@ -11816,10 +11816,10 @@
         <v>12</v>
       </c>
       <c r="AD109" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF109" t="n">
         <v>1.015856241684246</v>
@@ -11908,7 +11908,7 @@
         <v>0.03353610126413203</v>
       </c>
       <c r="Z110" t="n">
-        <v>0.04984271741778463</v>
+        <v>0.04984271741778462</v>
       </c>
       <c r="AA110" t="n">
         <v>0.04756872505273846</v>
@@ -11920,10 +11920,10 @@
         <v>12</v>
       </c>
       <c r="AD110" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF110" t="n">
         <v>1.015856241684246</v>
@@ -12024,10 +12024,10 @@
         <v>12</v>
       </c>
       <c r="AD111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF111" t="n">
         <v>0.0109662708441769</v>
@@ -12128,10 +12128,10 @@
         <v>12</v>
       </c>
       <c r="AD112" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF112" t="n">
         <v>1.011900948779371</v>
@@ -12232,10 +12232,10 @@
         <v>12</v>
       </c>
       <c r="AD113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF113" t="n">
         <v>0.1091083197419263</v>
@@ -12336,10 +12336,10 @@
         <v>12</v>
       </c>
       <c r="AD114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF114" t="n">
         <v>0.1091083197419263</v>
@@ -12428,7 +12428,7 @@
         <v>0.3516127352006783</v>
       </c>
       <c r="Z115" t="n">
-        <v>0.07867238633196715</v>
+        <v>0.07867238633196713</v>
       </c>
       <c r="AA115" t="n">
         <v>0.1222489091830135</v>
@@ -12440,10 +12440,10 @@
         <v>12</v>
       </c>
       <c r="AD115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF115" t="n">
         <v>1.040749636394338</v>
@@ -12544,10 +12544,10 @@
         <v>12</v>
       </c>
       <c r="AD116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF116" t="n">
         <v>1.138514196603143</v>
@@ -12648,10 +12648,10 @@
         <v>12</v>
       </c>
       <c r="AD117" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE117" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AF117" t="n">
         <v>0</v>
@@ -12740,7 +12740,7 @@
         <v>0.3852918737526619</v>
       </c>
       <c r="Z118" t="n">
-        <v>0.9788966232614135</v>
+        <v>0.9788966232614136</v>
       </c>
       <c r="AA118" t="n">
         <v>0.8192118431777171</v>
@@ -12752,10 +12752,10 @@
         <v>12</v>
       </c>
       <c r="AD118" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF118" t="n">
         <v>2.273070614392573</v>
@@ -12844,7 +12844,7 @@
         <v>1.330032948614527</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.292021738166569</v>
+        <v>1.292021738166568</v>
       </c>
       <c r="AA119" t="n">
         <v>0.03573073947480116</v>
@@ -12856,10 +12856,10 @@
         <v>12</v>
       </c>
       <c r="AD119" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AE119" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AF119" t="n">
         <v>0</v>
@@ -12948,7 +12948,7 @@
         <v>0.004720822473115449</v>
       </c>
       <c r="Z120" t="n">
-        <v>0.4128612939502298</v>
+        <v>0.4128612939502299</v>
       </c>
       <c r="AA120" t="n">
         <v>0.3507883378308808</v>
@@ -12960,10 +12960,10 @@
         <v>12</v>
       </c>
       <c r="AD120" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE120" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF120" t="n">
         <v>0</v>
@@ -13064,10 +13064,10 @@
         <v>12</v>
       </c>
       <c r="AD121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF121" t="n">
         <v>1.015263357974515</v>
@@ -13168,10 +13168,10 @@
         <v>12</v>
       </c>
       <c r="AD122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF122" t="n">
         <v>1.015263357974515</v>
@@ -13272,10 +13272,10 @@
         <v>12</v>
       </c>
       <c r="AD123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF123" t="n">
         <v>1.015263357974515</v>
@@ -13376,10 +13376,10 @@
         <v>12</v>
       </c>
       <c r="AD124" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF124" t="n">
         <v>1.015263357974515</v>
@@ -13468,7 +13468,7 @@
         <v>0</v>
       </c>
       <c r="Z125" t="n">
-        <v>0.01977541499901621</v>
+        <v>0.0197754149990162</v>
       </c>
       <c r="AA125" t="n">
         <v>0.04839631161908282</v>
@@ -13480,10 +13480,10 @@
         <v>12</v>
       </c>
       <c r="AD125" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF125" t="n">
         <v>1.016132103873028</v>
@@ -13572,7 +13572,7 @@
         <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>0.01977541499901621</v>
+        <v>0.0197754149990162</v>
       </c>
       <c r="AA126" t="n">
         <v>0.04839631161908282</v>
@@ -13584,10 +13584,10 @@
         <v>12</v>
       </c>
       <c r="AD126" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF126" t="n">
         <v>1.016132103873028</v>
@@ -13676,7 +13676,7 @@
         <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>0.01977541499901621</v>
+        <v>0.0197754149990162</v>
       </c>
       <c r="AA127" t="n">
         <v>0.04839631161908282</v>
@@ -13688,10 +13688,10 @@
         <v>12</v>
       </c>
       <c r="AD127" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF127" t="n">
         <v>1.016132103873028</v>
@@ -13780,7 +13780,7 @@
         <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>0.01977541499901621</v>
+        <v>0.0197754149990162</v>
       </c>
       <c r="AA128" t="n">
         <v>0.04839631161908282</v>
@@ -13792,10 +13792,10 @@
         <v>12</v>
       </c>
       <c r="AD128" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF128" t="n">
         <v>1.016132103873028</v>
@@ -13884,7 +13884,7 @@
         <v>0.03353610126413203</v>
       </c>
       <c r="Z129" t="n">
-        <v>0.04984271741778463</v>
+        <v>0.04984271741778462</v>
       </c>
       <c r="AA129" t="n">
         <v>0.04756872505273846</v>
@@ -13896,10 +13896,10 @@
         <v>12</v>
       </c>
       <c r="AD129" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF129" t="n">
         <v>1.015856241684246</v>
@@ -13988,7 +13988,7 @@
         <v>0.03353610126413203</v>
       </c>
       <c r="Z130" t="n">
-        <v>0.04984271741778463</v>
+        <v>0.04984271741778462</v>
       </c>
       <c r="AA130" t="n">
         <v>0.04756872505273846</v>
@@ -14000,10 +14000,10 @@
         <v>12</v>
       </c>
       <c r="AD130" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF130" t="n">
         <v>1.015856241684246</v>
@@ -14092,7 +14092,7 @@
         <v>0.03353610126413203</v>
       </c>
       <c r="Z131" t="n">
-        <v>0.04984271741778463</v>
+        <v>0.04984271741778462</v>
       </c>
       <c r="AA131" t="n">
         <v>0.04756872505273846</v>
@@ -14104,10 +14104,10 @@
         <v>12</v>
       </c>
       <c r="AD131" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE131" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF131" t="n">
         <v>1.015856241684246</v>
@@ -14196,7 +14196,7 @@
         <v>0.03353610126413203</v>
       </c>
       <c r="Z132" t="n">
-        <v>0.04984271741778463</v>
+        <v>0.04984271741778462</v>
       </c>
       <c r="AA132" t="n">
         <v>0.04756872505273846</v>
@@ -14208,10 +14208,10 @@
         <v>12</v>
       </c>
       <c r="AD132" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF132" t="n">
         <v>1.015856241684246</v>
@@ -14302,7 +14302,7 @@
         <v>0</v>
       </c>
       <c r="Z133" t="n">
-        <v>0.01977541499901621</v>
+        <v>0.0197754149990162</v>
       </c>
       <c r="AA133" t="n">
         <v>0.04839631161908282</v>
@@ -14314,10 +14314,10 @@
         <v>12</v>
       </c>
       <c r="AD133" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE133" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF133" t="n">
         <v>1.016132103873028</v>
@@ -14408,7 +14408,7 @@
         <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>0.01977541499901621</v>
+        <v>0.0197754149990162</v>
       </c>
       <c r="AA134" t="n">
         <v>0.04839631161908282</v>
@@ -14420,10 +14420,10 @@
         <v>12</v>
       </c>
       <c r="AD134" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF134" t="n">
         <v>1.016132103873028</v>
@@ -14514,7 +14514,7 @@
         <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>0.01977541499901621</v>
+        <v>0.0197754149990162</v>
       </c>
       <c r="AA135" t="n">
         <v>0.04839631161908282</v>
@@ -14526,10 +14526,10 @@
         <v>12</v>
       </c>
       <c r="AD135" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF135" t="n">
         <v>1.016132103873028</v>
@@ -14620,7 +14620,7 @@
         <v>0</v>
       </c>
       <c r="Z136" t="n">
-        <v>0.01977541499901621</v>
+        <v>0.0197754149990162</v>
       </c>
       <c r="AA136" t="n">
         <v>0.04839631161908282</v>
@@ -14632,10 +14632,10 @@
         <v>12</v>
       </c>
       <c r="AD136" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF136" t="n">
         <v>1.016132103873028</v>
